--- a/SAMMY COOOKIE.xlsx
+++ b/SAMMY COOOKIE.xlsx
@@ -2,38 +2,40 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ptctrolley\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47409D8C-B812-48D9-9EF9-4171172EF128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{054507E9-CEEB-4926-A03F-7DAA72E48A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{72983739-1824-4CAD-A101-DD06C1BF4C6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{72983739-1824-4CAD-A101-DD06C1BF4C6E}"/>
   </bookViews>
   <sheets>
     <sheet name="profit by country and cokiee" sheetId="9" r:id="rId1"/>
     <sheet name="Unit sold each month" sheetId="11" r:id="rId2"/>
-    <sheet name="Data" sheetId="1" r:id="rId3"/>
-    <sheet name="profit by month" sheetId="14" r:id="rId4"/>
-    <sheet name="New data" sheetId="2" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="3" r:id="rId6"/>
+    <sheet name="KPI" sheetId="15" r:id="rId3"/>
+    <sheet name="Data" sheetId="1" r:id="rId4"/>
+    <sheet name="profit by month" sheetId="14" r:id="rId5"/>
+    <sheet name="New data" sheetId="2" r:id="rId6"/>
+    <sheet name="Dashboard" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="KPI_Totals">KPI!$C$4</definedName>
     <definedName name="NativeTimeline_Date">#N/A</definedName>
     <definedName name="Slicer_Country">#N/A</definedName>
     <definedName name="Slicer_Product">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId8"/>
         <x14:slicerCache r:id="rId9"/>
+        <x14:slicerCache r:id="rId10"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -41,7 +43,7 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}">
       <x15:timelineCacheRefs>
-        <x15:timelineCacheRef r:id="rId10"/>
+        <x15:timelineCacheRef r:id="rId11"/>
       </x15:timelineCacheRefs>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -66,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2501" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="36">
   <si>
     <t>Country</t>
   </si>
@@ -172,18 +174,23 @@
   <si>
     <t>Dec</t>
   </si>
+  <si>
+    <t>Sum of Revenue</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="[$$-409]#,##0.00_ ;[Red]\-[$$-409]#,##0.00\ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +203,32 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Tw Cen MT Condensed"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -221,10 +254,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -237,11 +271,24 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="104">
+  <dxfs count="108">
     <dxf>
       <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     </dxf>
@@ -543,10 +590,22 @@
       <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
@@ -1055,7 +1114,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Fortune Cookie </c:v>
+                  <c:v> Chocolate Chip </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1072,23 +1131,47 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'profit by country and cokiee'!$A$5:$A$6</c:f>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'profit by country and cokiee'!$B$5:$B$6</c:f>
+              <c:f>'profit by country and cokiee'!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>25192</c:v>
+                  <c:v>234576</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>214821</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>208404</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>189846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>167082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1096,6 +1179,391 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-947E-4F47-BAF0-D7B8FFF8355B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> White Chocolate Macadamia Nut </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$C$5:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>105511.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>118982.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>116223.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86255</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100912.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-295F-4C05-A3AD-2A3AF3134878}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Oatmeal Raisin </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$D$5:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>81852.399999999994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88491.199999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99316</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>79508.800000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85722</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-295F-4C05-A3AD-2A3AF3134878}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Snickerdoodle </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$E$5:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>87012.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85142.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64547.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68060</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>62360</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-295F-4C05-A3AD-2A3AF3134878}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$F$3:$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Sugar </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$F$5:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>72187.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62608</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60376.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45725.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54479.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-295F-4C05-A3AD-2A3AF3134878}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$G$3:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Fortune Cookie </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$G$5:$G$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>25192.000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25026.399999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25290.400000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25403.200000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22448.799999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-295F-4C05-A3AD-2A3AF3134878}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1540,40 +2008,40 @@
                 <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>2228</c:v>
+                  <c:v>67841</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>488</c:v>
+                  <c:v>55115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1967</c:v>
+                  <c:v>53420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3803</c:v>
+                  <c:v>78893</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>200</c:v>
+                  <c:v>51771</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3226</c:v>
+                  <c:v>103302</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2666</c:v>
+                  <c:v>69355</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1830</c:v>
+                  <c:v>60705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1671</c:v>
+                  <c:v>107881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7179</c:v>
+                  <c:v>201104</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2321</c:v>
+                  <c:v>121131</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3911</c:v>
+                  <c:v>155306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1998,40 +2466,40 @@
                 <c:formatCode>"$"#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1782.4</c:v>
+                  <c:v>171317.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>390.4</c:v>
+                  <c:v>135968.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1573.6</c:v>
+                  <c:v>129483.05</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3042.4</c:v>
+                  <c:v>196765.94999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>160</c:v>
+                  <c:v>126856.84999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2580.8000000000002</c:v>
+                  <c:v>250815.45000000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2132.8000000000002</c:v>
+                  <c:v>173933.55000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1464</c:v>
+                  <c:v>153357.19999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1336.8000000000002</c:v>
+                  <c:v>265778.09999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5743.2</c:v>
+                  <c:v>484486.64999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1856.8</c:v>
+                  <c:v>289837.10000000003</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3128.8</c:v>
+                  <c:v>384764.6999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3388,7 +3856,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> Fortune Cookie </c:v>
+                  <c:v> Chocolate Chip </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3405,23 +3873,47 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'profit by country and cokiee'!$A$5:$A$6</c:f>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'profit by country and cokiee'!$B$5:$B$6</c:f>
+              <c:f>'profit by country and cokiee'!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>25192</c:v>
+                  <c:v>234576</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>214821</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>208404</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>189846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>167082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3429,6 +3921,391 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-2A87-443F-8DF3-CC7648C02326}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$C$3:$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> White Chocolate Macadamia Nut </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$C$5:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>105511.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>118982.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>116223.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86255</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100912.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A483-4E94-AE12-A0A6FBABA17E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$D$3:$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Oatmeal Raisin </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$D$5:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>81852.399999999994</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88491.199999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99316</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>79508.800000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85722</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A483-4E94-AE12-A0A6FBABA17E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$E$3:$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Snickerdoodle </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$E$5:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>87012.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85142.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64547.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68060</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>62360</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A483-4E94-AE12-A0A6FBABA17E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$F$3:$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Sugar </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$F$5:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>72187.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62608</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60376.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45725.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54479.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A483-4E94-AE12-A0A6FBABA17E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$G$3:$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Fortune Cookie </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'profit by country and cokiee'!$A$5:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>United Kingdom</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>United States</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Malaysia</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Philippines</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'profit by country and cokiee'!$G$5:$G$10</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>25192.000000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25026.399999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25290.400000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25403.200000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22448.799999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-A483-4E94-AE12-A0A6FBABA17E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4080,40 +4957,40 @@
                 <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>2228</c:v>
+                  <c:v>67841</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>488</c:v>
+                  <c:v>55115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1967</c:v>
+                  <c:v>53420</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3803</c:v>
+                  <c:v>78893</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>200</c:v>
+                  <c:v>51771</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3226</c:v>
+                  <c:v>103302</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2666</c:v>
+                  <c:v>69355</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1830</c:v>
+                  <c:v>60705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1671</c:v>
+                  <c:v>107881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7179</c:v>
+                  <c:v>201104</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2321</c:v>
+                  <c:v>121131</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3911</c:v>
+                  <c:v>155306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4732,40 +5609,40 @@
                 <c:formatCode>"$"#,##0</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1782.4</c:v>
+                  <c:v>171317.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>390.4</c:v>
+                  <c:v>135968.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1573.6</c:v>
+                  <c:v>129483.05</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3042.4</c:v>
+                  <c:v>196765.94999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>160</c:v>
+                  <c:v>126856.84999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2580.8000000000002</c:v>
+                  <c:v>250815.45000000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2132.8000000000002</c:v>
+                  <c:v>173933.55000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1464</c:v>
+                  <c:v>153357.19999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1336.8000000000002</c:v>
+                  <c:v>265778.09999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5743.2</c:v>
+                  <c:v>484486.64999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1856.8</c:v>
+                  <c:v>289837.10000000003</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3128.8</c:v>
+                  <c:v>384764.6999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8404,16 +9281,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>581023</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>160609</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>158310</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>158707</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>17341</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8443,15 +9320,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>65361</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>140575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>289034</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>91966</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8466,8 +9343,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3152775" y="495300"/>
-          <a:ext cx="10553700" cy="714375"/>
+          <a:off x="2942568" y="324506"/>
+          <a:ext cx="15384845" cy="1054977"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8495,25 +9372,34 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-GB" sz="3600" b="1">
+            <a:rPr lang="en-GB" sz="4800" b="1">
               <a:solidFill>
                 <a:schemeClr val="bg2"/>
               </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>SAMMY</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="3600" b="1" baseline="0">
+            <a:rPr lang="en-GB" sz="4800" b="1" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg2"/>
               </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t> COOKIE PERFORMANCE DASHBOARD</a:t>
           </a:r>
-          <a:endParaRPr lang="en-GB" sz="3600" b="1">
+          <a:endParaRPr lang="en-GB" sz="4800" b="1">
             <a:solidFill>
               <a:schemeClr val="bg2"/>
             </a:solidFill>
+            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8523,15 +9409,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>174625</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180974</xdr:rowOff>
+      <xdr:colOff>384833</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>154697</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>79375</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>71120</xdr:rowOff>
+      <xdr:colOff>289583</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>44844</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8561,15 +9447,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>164464</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>76834</xdr:rowOff>
+      <xdr:colOff>361533</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>89973</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>101599</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>30479</xdr:rowOff>
+      <xdr:colOff>298668</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>43617</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8598,19 +9484,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>145445</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>145143</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>234782</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>153026</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>280736</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>156784</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1246908</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>164667</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-      <mc:Choice Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Date">
@@ -8628,12 +9514,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer name="Date"/>
+              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Date"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8643,8 +9529,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="145445" y="1446119"/>
-              <a:ext cx="1975242" cy="1312616"/>
+              <a:off x="2063582" y="4115426"/>
+              <a:ext cx="2092781" cy="1272405"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8675,19 +9561,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>126705</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>126649</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>273611</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>174663</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>290763</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>20053</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1274617</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>138547</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Country">
@@ -8710,7 +9596,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8720,8 +9606,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="126705" y="4772990"/>
-              <a:ext cx="2004009" cy="1566087"/>
+              <a:off x="2102411" y="7379027"/>
+              <a:ext cx="2081661" cy="1404756"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8753,19 +9639,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>140305</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>45811</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>258785</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>70653</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>280737</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>80211</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1246909</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>105053</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="Product">
@@ -8788,7 +9674,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8798,8 +9684,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="140305" y="2833616"/>
-              <a:ext cx="1980383" cy="1892936"/>
+              <a:off x="2087585" y="5473926"/>
+              <a:ext cx="2068779" cy="1835491"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8827,6 +9713,325 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>875387</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>397</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>554823</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>64096</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="KPI!E19">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D9370D8-A042-D91B-FF35-EB07B7C3E538}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3784842" y="1967742"/>
+          <a:ext cx="2824417" cy="1144354"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:fld id="{A3EBE2E9-F7A0-49B0-80C0-06B170A2B0E3}" type="TxLink">
+            <a:rPr lang="en-US" sz="2400" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>TOTAL REVENUE
+$4,690,319.00</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-GB" sz="2400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>531092</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>289034</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>557369</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>52551</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="KPI!E20">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectangle 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{910EC856-264D-474E-B815-B33D60D9F4FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7195128" y="1965434"/>
+          <a:ext cx="2852605" cy="1135117"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:fld id="{8986B6BD-2F3E-4DC7-8F6F-4159492B2D35}" type="TxLink">
+            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>TOTAL PROFIT
+$2,763,364.45</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-GB" sz="2800" b="1">
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>170476</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>289034</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>430609</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>52551</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="KPI!E21">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Rectangle 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{416F8CEB-0229-4413-A529-B30D0E3648E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10880040" y="1965434"/>
+          <a:ext cx="2850933" cy="1135117"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:fld id="{BC298A3D-4C4D-4DB8-B3E2-D153D2B1F949}" type="TxLink">
+            <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>TOTAL UNITS SOLD
+1,125,824</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-GB" sz="2000" b="1">
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>542468</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>289034</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>340146</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>60171</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="KPI!E22">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Rectangle 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A2B84E-7962-4697-8C29-F5FB58646428}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14452432" y="1965434"/>
+          <a:ext cx="2845678" cy="1142737"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:fld id="{A39AAC8C-FFB6-4A1C-BB35-65CC2B451BAE}" type="TxLink">
+            <a:rPr lang="en-US" sz="2400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>PROFIT MARGIN
+58.92%</a:t>
+          </a:fld>
+          <a:endParaRPr lang="en-GB" sz="2400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -15605,16 +16810,16 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5E6B0CE-D14E-42C0-BFA7-F2B4D934EFF4}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:C6" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5E6B0CE-D14E-42C0-BFA7-F2B4D934EFF4}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:H10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="6">
         <item x="0"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -15629,12 +16834,12 @@
     </pivotField>
     <pivotField axis="axisCol" multipleItemSelectionAllowed="1" showAll="0" sortType="descending">
       <items count="7">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -16068,9 +17273,21 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="6">
     <i>
       <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -16079,7 +17296,22 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
     <i>
       <x v="1"/>
     </i>
@@ -16091,14 +17323,14 @@
     <dataField name="Sum of Profit" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="103">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="102">
+    <format dxfId="3">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -16279,27 +17511,27 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4D7C0C4-E5A0-45BE-96DB-00D143F876A6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4D7C0C4-E5A0-45BE-96DB-00D143F876A6}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0">
       <items count="6">
         <item x="0"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -16773,11 +18005,11 @@
     <dataField name="Sum of Units Sold" fld="2" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="101">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="4">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -16787,25 +18019,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
     <chartFormat chart="5" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="13" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -16828,27 +18042,131 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{171B6B5A-A5CC-47F4-9B30-5A6166EA689A}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59DFE4C6-05CE-4823-B533-A3ED0351F49E}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C4" firstHeaderRow="0" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="9">
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0">
+      <items count="17">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="11"/>
+        <item x="5"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of Revenue" fld="3" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Sum of Profit" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Sum of Units Sold" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{171B6B5A-A5CC-47F4-9B30-5A6166EA689A}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0">
       <items count="6">
         <item x="0"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -17321,11 +18639,11 @@
     <dataField name="Sum of Profit" fld="5" baseField="0" baseItem="0" numFmtId="166"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="100">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="4">
+  <chartFormats count="3">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -17336,15 +18654,6 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -17381,15 +18690,16 @@
     <pivotTable tabId="9" name="PivotTable3"/>
     <pivotTable tabId="14" name="PivotTable3"/>
     <pivotTable tabId="11" name="PivotTable3"/>
+    <pivotTable tabId="15" name="PivotTable1"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="46708581">
       <items count="5">
         <i x="0" s="1"/>
-        <i x="3"/>
-        <i x="2"/>
-        <i x="1"/>
-        <i x="4"/>
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
+        <i x="4" s="1"/>
       </items>
     </tabular>
   </data>
@@ -17402,16 +18712,17 @@
     <pivotTable tabId="9" name="PivotTable3"/>
     <pivotTable tabId="14" name="PivotTable3"/>
     <pivotTable tabId="11" name="PivotTable3"/>
+    <pivotTable tabId="15" name="PivotTable1"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="46708581">
       <items count="6">
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="1" s="1"/>
-        <i x="2"/>
-        <i x="3"/>
-        <i x="4"/>
-        <i x="5"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
+        <i x="5" s="1"/>
       </items>
     </tabular>
   </data>
@@ -17746,6 +19057,7 @@
     <pivotTable tabId="9" name="PivotTable3"/>
     <pivotTable tabId="14" name="PivotTable3"/>
     <pivotTable tabId="11" name="PivotTable3"/>
+    <pivotTable tabId="15" name="PivotTable1"/>
   </pivotTables>
   <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="46708581" filterType="unknown">
     <bounds startDate="2019-01-01T00:00:00" endDate="2021-01-01T00:00:00"/>
@@ -17755,28 +19067,28 @@
 
 <file path=xl/timelines/timeline1.xml><?xml version="1.0" encoding="utf-8"?>
 <timelines xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <timeline name="Date" xr10:uid="{8D7B085D-A3BA-4A05-916C-94E4CDA2DEF9}" cache="NativeTimeline_Date" caption="Date" level="2" selectionLevel="2" scrollPosition="2019-01-01T00:00:00"/>
+  <timeline name="Date" xr10:uid="{8D7B085D-A3BA-4A05-916C-94E4CDA2DEF9}" cache="NativeTimeline_Date" caption="Date" level="2" selectionLevel="2" scrollPosition="2019-09-01T00:00:00"/>
 </timelines>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479C2525-68E3-4C38-BB1B-A873FA93C6FE}">
-  <dimension ref="A3:C6"/>
+  <dimension ref="A3:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="25" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="176" max="176" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -17784,37 +19096,186 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="6">
-        <v>25192</v>
+        <v>234576</v>
       </c>
       <c r="C5" s="6">
-        <v>25192</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>105511.25</v>
+      </c>
+      <c r="D5" s="6">
+        <v>81852.399999999994</v>
+      </c>
+      <c r="E5" s="6">
+        <v>87012.5</v>
+      </c>
+      <c r="F5" s="6">
+        <v>72187.5</v>
+      </c>
+      <c r="G5" s="6">
+        <v>25192.000000000004</v>
+      </c>
+      <c r="H5" s="6">
+        <v>606331.65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="6">
+        <v>214821</v>
+      </c>
+      <c r="C6" s="6">
+        <v>118982.5</v>
+      </c>
+      <c r="D6" s="6">
+        <v>88491.199999999997</v>
+      </c>
+      <c r="E6" s="6">
+        <v>85142.5</v>
+      </c>
+      <c r="F6" s="6">
+        <v>62608</v>
+      </c>
+      <c r="G6" s="6">
+        <v>25026.399999999998</v>
+      </c>
+      <c r="H6" s="6">
+        <v>595071.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="6">
+        <v>208404</v>
+      </c>
+      <c r="C7" s="6">
+        <v>116223.25</v>
+      </c>
+      <c r="D7" s="6">
+        <v>99316</v>
+      </c>
+      <c r="E7" s="6">
+        <v>64547.5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>60376.75</v>
+      </c>
+      <c r="G7" s="6">
+        <v>25290.400000000001</v>
+      </c>
+      <c r="H7" s="6">
+        <v>574157.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6">
+        <v>189846</v>
+      </c>
+      <c r="C8" s="6">
+        <v>86255</v>
+      </c>
+      <c r="D8" s="6">
+        <v>79508.800000000003</v>
+      </c>
+      <c r="E8" s="6">
+        <v>68060</v>
+      </c>
+      <c r="F8" s="6">
+        <v>45725.75</v>
+      </c>
+      <c r="G8" s="6">
+        <v>25403.200000000001</v>
+      </c>
+      <c r="H8" s="6">
+        <v>494798.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6">
+        <v>167082</v>
+      </c>
+      <c r="C9" s="6">
+        <v>100912.5</v>
+      </c>
+      <c r="D9" s="6">
+        <v>85722</v>
+      </c>
+      <c r="E9" s="6">
+        <v>62360</v>
+      </c>
+      <c r="F9" s="6">
+        <v>54479.25</v>
+      </c>
+      <c r="G9" s="6">
+        <v>22448.799999999999</v>
+      </c>
+      <c r="H9" s="6">
+        <v>493004.55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="6">
-        <v>25192</v>
-      </c>
-      <c r="C6" s="6">
-        <v>25192</v>
+      <c r="B10" s="6">
+        <v>1014729</v>
+      </c>
+      <c r="C10" s="6">
+        <v>527884.5</v>
+      </c>
+      <c r="D10" s="6">
+        <v>434890.4</v>
+      </c>
+      <c r="E10" s="6">
+        <v>367122.5</v>
+      </c>
+      <c r="F10" s="6">
+        <v>295377.25</v>
+      </c>
+      <c r="G10" s="6">
+        <v>123360.79999999999</v>
+      </c>
+      <c r="H10" s="6">
+        <v>2763364.4499999997</v>
       </c>
     </row>
   </sheetData>
@@ -17847,7 +19308,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="7">
-        <v>2228</v>
+        <v>67841</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -17855,7 +19316,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="7">
-        <v>488</v>
+        <v>55115</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -17863,7 +19324,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="7">
-        <v>1967</v>
+        <v>53420</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -17871,7 +19332,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="7">
-        <v>3803</v>
+        <v>78893</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -17879,7 +19340,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="7">
-        <v>200</v>
+        <v>51771</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -17887,7 +19348,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="7">
-        <v>3226</v>
+        <v>103302</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -17895,7 +19356,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="7">
-        <v>2666</v>
+        <v>69355</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -17903,7 +19364,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="7">
-        <v>1830</v>
+        <v>60705</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -17911,7 +19372,7 @@
         <v>31</v>
       </c>
       <c r="B12" s="7">
-        <v>1671</v>
+        <v>107881</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -17919,7 +19380,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="7">
-        <v>7179</v>
+        <v>201104</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -17927,7 +19388,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="7">
-        <v>2321</v>
+        <v>121131</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -17935,7 +19396,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="7">
-        <v>3911</v>
+        <v>155306</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -17943,7 +19404,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="7">
-        <v>31490</v>
+        <v>1125824</v>
       </c>
     </row>
   </sheetData>
@@ -17953,6 +19414,71 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9518DF38-0680-45FE-85FF-345E158F5694}">
+  <dimension ref="A3:E22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>4690319</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2763364.4500000007</v>
+      </c>
+      <c r="C4" s="18">
+        <v>1125824</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E19" t="str">
+        <f>"TOTAL REVENUE"&amp;CHAR(10)&amp;TEXT(A4,"$#,##0.00")</f>
+        <v>TOTAL REVENUE
+$4,690,319.00</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E20" t="str">
+        <f>"TOTAL PROFIT"&amp;CHAR(10)&amp;TEXT(B4,"$#,##0.00")</f>
+        <v>TOTAL PROFIT
+$2,763,364.45</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E21" t="str">
+        <f>"TOTAL UNITS SOLD"&amp;CHAR(10)&amp;TEXT(C4,"#,##0")</f>
+        <v>TOTAL UNITS SOLD
+1,125,824</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E22" t="str">
+        <f>"PROFIT MARGIN"&amp;CHAR(10)&amp;TEXT(IFERROR(B4/A4,0),"0.00%")</f>
+        <v>PROFIT MARGIN
+58.92%</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{960989E7-AA73-48E8-824F-3B1ACE91DEAF}">
   <dimension ref="A1:G701"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -34088,7 +35614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18AB5BB1-4F74-44D1-A13C-41E06B3A77EF}">
   <dimension ref="A3:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -34112,7 +35638,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="6">
-        <v>1782.4</v>
+        <v>171317.6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -34120,7 +35646,7 @@
         <v>24</v>
       </c>
       <c r="B5" s="6">
-        <v>390.4</v>
+        <v>135968.25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -34128,7 +35654,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="6">
-        <v>1573.6</v>
+        <v>129483.05</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -34136,7 +35662,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="6">
-        <v>3042.4</v>
+        <v>196765.94999999998</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -34144,7 +35670,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="6">
-        <v>160</v>
+        <v>126856.84999999999</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -34152,7 +35678,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="6">
-        <v>2580.8000000000002</v>
+        <v>250815.45000000004</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -34160,7 +35686,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="6">
-        <v>2132.8000000000002</v>
+        <v>173933.55000000002</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -34168,7 +35694,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="6">
-        <v>1464</v>
+        <v>153357.19999999998</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -34176,7 +35702,7 @@
         <v>31</v>
       </c>
       <c r="B12" s="6">
-        <v>1336.8000000000002</v>
+        <v>265778.09999999998</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -34184,7 +35710,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="6">
-        <v>5743.2</v>
+        <v>484486.64999999997</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -34192,7 +35718,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="6">
-        <v>1856.8</v>
+        <v>289837.10000000003</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -34200,7 +35726,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="6">
-        <v>3128.8</v>
+        <v>384764.6999999999</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -34208,7 +35734,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="6">
-        <v>25192</v>
+        <v>2763364.4499999997</v>
       </c>
     </row>
   </sheetData>
@@ -34217,7 +35743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{591501D7-BD89-4E84-A971-559DEF565CA2}">
   <dimension ref="A1:G526"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -46328,11 +47854,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF38B5E9-6609-42B5-96BC-813A6776C699}">
-  <dimension ref="A1"/>
+  <dimension ref="F8:Y17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="6.77734375" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="8" spans="6:18" ht="32.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="F8" s="17"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="12"/>
+    </row>
+    <row r="9" spans="6:18" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="16"/>
+    </row>
+    <row r="10" spans="6:18" x14ac:dyDescent="0.3">
+      <c r="F10" s="8"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="17" spans="25:25" ht="29.4" x14ac:dyDescent="0.45">
+      <c r="Y17" s="19"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <extLst>
